--- a/reports/executive_slides.xlsx
+++ b/reports/executive_slides.xlsx
@@ -42,7 +42,7 @@
     <t xml:space="preserve">Executive deck - companion workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Every figure and table from executive_slides.Rmd, in slide order (generated 2026-08-31 21:28).</t>
+    <t xml:space="preserve">Every figure and table from executive_slides.Rmd, in slide order (generated 2026-09-01 11:29).</t>
   </si>
   <si>
     <t xml:space="preserve">#</t>
@@ -1434,7 +1434,7 @@
       <xdr:row xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">4</xdr:row>
       <xdr:rowOff xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">0</xdr:rowOff>
     </xdr:from>
-    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="7315200" cy="5486400"/>
+    <xdr:ext xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" cx="12070080" cy="5486400"/>
     <xdr:pic xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
       <xdr:nvPicPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
         <xdr:cNvPr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" id="1" name="Picture 1"/>
